--- a/product_selector_out/STM32L4R9-S9.xlsx
+++ b/product_selector_out/STM32L4R9-S9.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,17 +61,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -103,8 +93,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1234,7 +1222,7 @@
       </c>
       <c r="AW12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX12" s="4" t="inlineStr">
@@ -1314,7 +1302,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1549,7 @@
       </c>
       <c r="AW13" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX13" s="4" t="inlineStr">
@@ -1641,7 +1629,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1876,7 @@
       </c>
       <c r="AW14" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX14" s="4" t="inlineStr">
@@ -1968,7 +1956,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2203,7 @@
       </c>
       <c r="AW15" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX15" s="4" t="inlineStr">
@@ -2295,7 +2283,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2530,7 @@
       </c>
       <c r="AW16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX16" s="4" t="inlineStr">
@@ -2622,7 +2610,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2857,7 @@
       </c>
       <c r="AW17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX17" s="4" t="inlineStr">
@@ -2949,7 +2937,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3184,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -3276,7 +3264,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3511,7 @@
       </c>
       <c r="AW19" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX19" s="4" t="inlineStr">
@@ -3603,7 +3591,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3838,7 @@
       </c>
       <c r="AW20" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AX20" s="4" t="inlineStr">
@@ -3930,7 +3918,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4541,9 +4529,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -4556,17 +4544,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4581,7 +4569,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4591,29 +4579,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -4631,22 +4619,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4671,12 +4659,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="8" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4691,7 +4679,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="8" t="inlineStr">
+      <c r="AI12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4701,7 +4689,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="8" t="inlineStr">
+      <c r="AK12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4746,29 +4734,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -4791,42 +4779,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4841,9 +4829,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4868,9 +4856,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4883,17 +4871,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4908,7 +4896,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4918,29 +4906,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -4958,22 +4946,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4998,12 +4986,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="8" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5018,7 +5006,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="8" t="inlineStr">
+      <c r="AI13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5028,7 +5016,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="8" t="inlineStr">
+      <c r="AK13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5073,29 +5061,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -5118,42 +5106,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5168,9 +5156,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5195,9 +5183,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -5210,17 +5198,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5235,7 +5223,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5245,29 +5233,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -5285,22 +5273,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5315,7 +5303,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AC14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5325,12 +5313,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="8" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5345,7 +5333,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="8" t="inlineStr">
+      <c r="AI14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5355,7 +5343,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="8" t="inlineStr">
+      <c r="AK14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5400,29 +5388,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -5445,42 +5433,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5495,9 +5483,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5522,9 +5510,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -5537,17 +5525,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5562,7 +5550,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5572,29 +5560,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -5612,22 +5600,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5652,12 +5640,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="8" t="inlineStr">
+      <c r="AE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5672,7 +5660,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="8" t="inlineStr">
+      <c r="AI15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5682,7 +5670,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="8" t="inlineStr">
+      <c r="AK15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5727,29 +5715,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -5772,42 +5760,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5822,9 +5810,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5849,9 +5837,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -5864,17 +5852,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5889,7 +5877,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5899,29 +5887,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -5939,22 +5927,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5969,7 +5957,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="8" t="inlineStr">
+      <c r="AC16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5979,12 +5967,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="8" t="inlineStr">
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5999,7 +5987,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="8" t="inlineStr">
+      <c r="AI16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6009,7 +5997,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="8" t="inlineStr">
+      <c r="AK16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6054,29 +6042,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -6099,42 +6087,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6149,9 +6137,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6176,9 +6164,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -6191,17 +6179,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6216,7 +6204,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6226,29 +6214,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -6266,22 +6254,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6306,12 +6294,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="8" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6326,7 +6314,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="8" t="inlineStr">
+      <c r="AI17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6336,7 +6324,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="8" t="inlineStr">
+      <c r="AK17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6381,29 +6369,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -6426,42 +6414,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6476,9 +6464,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6503,9 +6491,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -6518,17 +6506,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6543,7 +6531,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6553,29 +6541,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -6593,22 +6581,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6633,12 +6621,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="8" t="inlineStr">
+      <c r="AE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6653,7 +6641,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="8" t="inlineStr">
+      <c r="AI18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6663,7 +6651,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="8" t="inlineStr">
+      <c r="AK18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6708,29 +6696,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -6753,42 +6741,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
+      <c r="BC18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6803,9 +6791,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6830,9 +6818,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -6845,17 +6833,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="8" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6870,7 +6858,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6880,29 +6868,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -6920,22 +6908,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6960,12 +6948,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="8" t="inlineStr">
+      <c r="AE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6980,7 +6968,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="8" t="inlineStr">
+      <c r="AI19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6990,7 +6978,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK19" s="8" t="inlineStr">
+      <c r="AK19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7035,29 +7023,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -7080,42 +7068,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
+      <c r="BC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7130,9 +7118,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7157,9 +7145,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -7172,17 +7160,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7197,7 +7185,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="M20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7207,29 +7195,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -7247,22 +7235,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="8" t="inlineStr">
+      <c r="W20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7287,12 +7275,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="8" t="inlineStr">
+      <c r="AE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7307,7 +7295,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="8" t="inlineStr">
+      <c r="AI20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7317,7 +7305,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="8" t="inlineStr">
+      <c r="AK20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7362,29 +7350,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AT20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -7407,42 +7395,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="8" t="inlineStr">
+      <c r="BC20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7457,9 +7445,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7509,402 +7497,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STM32L4R9ZI</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STM32L4R9ZI</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32L4R9ZG</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32L4R9ZG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32L4R9AG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32L4R9AG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32L4R9VG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32L4R9VG</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32L4S9AI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32L4S9AI</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32L4R9AI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32L4R9AI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32L4S9ZI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32L4S9ZI</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32L4S9VI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32L4S9VI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32L4R9VI</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32L4R9VI</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L4R9-S9.xlsx
+++ b/product_selector_out/STM32L4R9-S9.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,7 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -93,6 +103,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1302,7 +1314,7 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1641,7 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2295,7 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2622,7 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3603,7 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
@@ -4529,9 +4541,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -4544,17 +4556,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4569,7 +4581,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4579,29 +4591,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -4619,22 +4631,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4659,12 +4671,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF12" s="7" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4679,7 +4691,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI12" s="7" t="inlineStr">
+      <c r="AI12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4689,7 +4701,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK12" s="7" t="inlineStr">
+      <c r="AK12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4734,29 +4746,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY12" s="6" t="inlineStr">
@@ -4779,42 +4791,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4829,9 +4841,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4856,9 +4868,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4871,17 +4883,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4896,7 +4908,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4906,29 +4918,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -4946,22 +4958,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4986,12 +4998,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF13" s="7" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5006,7 +5018,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI13" s="7" t="inlineStr">
+      <c r="AI13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5016,7 +5028,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK13" s="7" t="inlineStr">
+      <c r="AK13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5061,29 +5073,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -5106,42 +5118,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5156,9 +5168,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5183,9 +5195,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -5198,17 +5210,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5223,7 +5235,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5233,29 +5245,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -5273,22 +5285,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5303,7 +5315,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="7" t="inlineStr">
+      <c r="AC14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5313,12 +5325,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF14" s="7" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5333,7 +5345,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI14" s="7" t="inlineStr">
+      <c r="AI14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5343,7 +5355,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK14" s="7" t="inlineStr">
+      <c r="AK14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5388,29 +5400,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY14" s="6" t="inlineStr">
@@ -5433,42 +5445,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5483,9 +5495,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5510,9 +5522,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -5525,17 +5537,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5550,7 +5562,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5560,29 +5572,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -5600,22 +5612,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5640,12 +5652,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF15" s="7" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5660,7 +5672,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI15" s="7" t="inlineStr">
+      <c r="AI15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5670,7 +5682,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK15" s="7" t="inlineStr">
+      <c r="AK15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5715,29 +5727,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY15" s="6" t="inlineStr">
@@ -5760,42 +5772,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5810,9 +5822,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5837,9 +5849,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -5852,17 +5864,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5877,7 +5889,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5887,29 +5899,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -5927,22 +5939,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5957,7 +5969,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="7" t="inlineStr">
+      <c r="AC16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5967,12 +5979,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF16" s="7" t="inlineStr">
+      <c r="AE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5987,7 +5999,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI16" s="7" t="inlineStr">
+      <c r="AI16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5997,7 +6009,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK16" s="7" t="inlineStr">
+      <c r="AK16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6042,29 +6054,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY16" s="6" t="inlineStr">
@@ -6087,42 +6099,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6137,9 +6149,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6164,9 +6176,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -6179,17 +6191,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6204,7 +6216,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6214,29 +6226,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -6254,22 +6266,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6294,12 +6306,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF17" s="7" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6314,7 +6326,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI17" s="7" t="inlineStr">
+      <c r="AI17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6324,7 +6336,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK17" s="7" t="inlineStr">
+      <c r="AK17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6369,29 +6381,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY17" s="6" t="inlineStr">
@@ -6414,42 +6426,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6464,9 +6476,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6491,9 +6503,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -6506,17 +6518,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6531,7 +6543,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6541,29 +6553,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -6581,22 +6593,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6621,12 +6633,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF18" s="7" t="inlineStr">
+      <c r="AE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6641,7 +6653,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI18" s="7" t="inlineStr">
+      <c r="AI18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6651,7 +6663,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK18" s="7" t="inlineStr">
+      <c r="AK18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6696,29 +6708,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -6741,42 +6753,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="7" t="inlineStr">
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6791,9 +6803,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6818,9 +6830,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -6833,17 +6845,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6858,7 +6870,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6868,29 +6880,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -6908,22 +6920,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6948,12 +6960,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF19" s="7" t="inlineStr">
+      <c r="AE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6968,7 +6980,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI19" s="7" t="inlineStr">
+      <c r="AI19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6978,7 +6990,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK19" s="7" t="inlineStr">
+      <c r="AK19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7023,29 +7035,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY19" s="6" t="inlineStr">
@@ -7068,42 +7080,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="7" t="inlineStr">
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7118,9 +7130,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7145,9 +7157,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -7160,17 +7172,17 @@
           <t>API</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7185,7 +7197,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7195,29 +7207,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -7235,22 +7247,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="Z20" s="7" t="inlineStr">
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="Z20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7275,12 +7287,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AF20" s="7" t="inlineStr">
+      <c r="AE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AF20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7295,7 +7307,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AI20" s="7" t="inlineStr">
+      <c r="AI20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7305,7 +7317,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AK20" s="7" t="inlineStr">
+      <c r="AK20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7350,29 +7362,29 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AT20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AU20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AV20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AW20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AT20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AU20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AV20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY20" s="6" t="inlineStr">
@@ -7395,42 +7407,42 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ20" s="7" t="inlineStr">
+      <c r="BC20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ20" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -7445,9 +7457,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7466,7 +7478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7497,7 +7509,600 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32L4R9ZI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32L4R9ZI</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32L4R9ZI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32L4R9ZG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32L4R9ZG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32L4R9ZG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L4R9AG</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L4R9AG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L4R9AG</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L4R9VG</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L4R9VG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L4R9VG</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L4S9AI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L4S9AI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L4S9AI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32L4R9AI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L4R9AI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L4R9AI</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L4S9ZI</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L4S9ZI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32L4S9ZI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L4S9VI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32L4S9VI</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32L4S9VI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32L4R9VI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32L4R9VI</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 10. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32L4R9VI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1(.17)1' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L4R9-S9.xlsx
+++ b/product_selector_out/STM32L4R9-S9.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM20"/>
+  <dimension ref="A1:BN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.578125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -3930,12 +3977,17 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -3956,16 +4008,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3978,6 +4028,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3997,7 +4048,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -4023,7 +4076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM20"/>
+  <dimension ref="A1:BN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4091,6 +4144,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4424,6 +4478,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4519,6 +4578,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4841,7 +4901,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5168,7 +5233,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5495,7 +5565,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5822,7 +5897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6149,7 +6229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6476,7 +6561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6803,7 +6893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7130,7 +7225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7457,7 +7557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7465,8 +7570,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
